--- a/jogos_2024-09-30.xlsx
+++ b/jogos_2024-09-30.xlsx
@@ -1536,58 +1536,58 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vorskla</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -1596,59 +1596,59 @@
         <v>2.63</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['12', '61']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.19</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['45', '85']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.38</v>
+        <v>1.74</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45565.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>2.12</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['35', '60', '71']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.88</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['12', '61']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.74</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45565.5</v>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Vorskla</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['45', '85']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.32</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AH11" t="n">
         <v>1.5</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['35', '60', '71']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45565.5</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
         <v>4.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['18', '43', '45', '51', '64']</t>
+          <t>['15', '57', '78']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45565.54166666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,55 +2088,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O13" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.88</v>
       </c>
       <c r="P13" t="n">
         <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC13" t="n">
         <v>1.83</v>
@@ -2146,25 +2146,25 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['50', '75']</t>
+          <t>['43', '74']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45565.54166666666</v>
@@ -2310,119 +2310,119 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['12', '79', '86']</t>
+          <t>['31', '35', '64', '84']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['44', '48', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.16</v>
+        <v>4.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45565.54166666666</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.4</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>15</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['31', '35', '64', '84']</t>
+          <t>['18', '43', '45', '51', '64']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45565.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
         <v>1.44</v>
@@ -2634,13 +2634,13 @@
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="Y17" t="n">
         <v>2.1</v>
@@ -2649,38 +2649,38 @@
         <v>1.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.44</v>
+        <v>3.71</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['43', '74']</t>
+          <t>['12', '79', '86']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '48', '84']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45565.54166666666</v>
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['50', '75']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.65</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="AI18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['15', '57', '78']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45565.54166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,23 +2965,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
@@ -2991,55 +2991,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
         <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
         <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC20" t="n">
         <v>1.67</v>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45565.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.6</v>
       </c>
-      <c r="N21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45565.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
         <v>3</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.06</v>
+        <v>3.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['18', '21', '25', '34']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45565.58333333334</v>
@@ -3342,26 +3342,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Lamia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>2</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X23" t="n">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['6', '89']</t>
+          <t>['36', '63']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45565.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="X25" t="n">
-        <v>4.3</v>
+        <v>2.73</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>3.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['5', '9', '25']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['56', '78', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45565.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>23</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="U26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2.75</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA26" t="n">
-        <v>2.65</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['56', '74']</t>
+          <t>['57', '65']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.63</v>
+        <v>6.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45565.58333333334</v>
@@ -3987,35 +3987,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>17</v>
+      </c>
+      <c r="M28" t="n">
+        <v>8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O28" t="n">
+        <v>13</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.5</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.72</v>
+        <v>2.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4086,20 +4086,20 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['5', '9', '25']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45565.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>17</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>1.11</v>
+        <v>6.75</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>1.81</v>
       </c>
       <c r="P29" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.44</v>
+        <v>6.93</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA29" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '24', '72', '78', '88']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['74', '80']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>3.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45565.58333333334</v>
@@ -4245,91 +4245,91 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="T30" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="U30" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
         <v>1.67</v>
@@ -4339,25 +4339,25 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '89']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45565.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>23</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="P32" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['57', '65']</t>
+          <t>['56', '74']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ32" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45565.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>2.4</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1.5</v>
       </c>
-      <c r="S33" t="n">
+      <c r="AD33" t="n">
         <v>2.5</v>
       </c>
-      <c r="T33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '21', '25', '34']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45565.58333333334</v>
@@ -4761,58 +4761,58 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O34" t="n">
         <v>5</v>
       </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.81</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.93</v>
+        <v>2.1</v>
       </c>
       <c r="R34" t="n">
         <v>1.29</v>
@@ -4821,59 +4821,59 @@
         <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD34" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['21', '24', '72', '78', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['74', '80']</t>
+          <t>['56', '78', '90+1']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.08</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.7</v>
+        <v>1.16</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45565.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lamia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="n">
-        <v>2</v>
-      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
         <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X35" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.65</v>
+        <v>4.23</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
           <t>['67']</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['36', '63']</t>
-        </is>
-      </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45565.58333333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['38', '42', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X40" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45565.625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X41" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA41" t="n">
         <v>2</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>7</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['38', '42', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45565.625</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y47" t="n">
         <v>1.83</v>
       </c>
-      <c r="P47" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>7</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="Z47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1.4</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['27', '37', '40', '59']</t>
+          <t>['62', '87']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['34', '75', '87']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45565.65625</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="O48" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S48" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="T48" t="n">
         <v>3.75</v>
       </c>
-      <c r="R48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="X48" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AA48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['62', '87']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['34', '75', '87']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45565.65625</v>
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M49" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O49" t="n">
         <v>2.75</v>
       </c>
-      <c r="O49" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P49" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['7', '11', '24']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['49', '83']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.5</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD49" t="n">
+      <c r="AI49" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ49" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45565.65625</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,22 +6835,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA50" t="n">
         <v>3.6</v>
       </c>
-      <c r="N50" t="n">
-        <v>5</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.82</v>
-      </c>
       <c r="AB50" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC50" t="n">
         <v>1.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['65', '80']</t>
+          <t>['6', '67', '78']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45565.65625</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N51" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="O51" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
         <v>1.4</v>
@@ -7014,13 +7014,13 @@
         <v>2.75</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W51" t="n">
         <v>1.25</v>
@@ -7029,10 +7029,10 @@
         <v>3.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA51" t="n">
         <v>3.3</v>
@@ -7048,25 +7048,25 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['7', '11', '24']</t>
+          <t>['27', '37', '40', '59']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['49', '83']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45565.65625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P52" t="n">
         <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S52" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V52" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W52" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X52" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AC52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD52" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD52" t="n">
-        <v>2</v>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['6', '67', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45565.65625</v>
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="T53" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U53" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V53" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="X53" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AA53" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['65', '80']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45565.65625</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,22 +7351,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="M54" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O54" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q54" t="n">
         <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>2.25</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45565.65625</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7495,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="M55" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P55" t="n">
         <v>2.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R55" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S55" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD55" t="n">
         <v>2.25</v>
       </c>
-      <c r="U55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['45', '84', '90+7']</t>
+          <t>['17', '32', '39']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45565.66666666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7624,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="M56" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N56" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="P56" t="n">
         <v>2.5</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T56" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U56" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V56" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W56" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X56" t="n">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['17', '32', '39']</t>
+          <t>['45', '84', '90+7']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45565.66666666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="O65" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T65" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U65" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V65" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="X65" t="n">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.33</v>
+        <v>2.97</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.45</v>
+        <v>1.21</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AJ65" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45565.875</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,25 +8899,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="P66" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y66" t="n">
         <v>2.5</v>
       </c>
-      <c r="R66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X66" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z66" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.21</v>
+        <v>2.45</v>
       </c>
       <c r="AI66" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45565.875</v>
@@ -9147,35 +9147,35 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N68" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="O68" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="R68" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="S68" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T68" t="n">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="U68" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V68" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W68" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="X68" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['46', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AI68" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ68" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45565.89583333334</v>
@@ -9276,35 +9276,35 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>['46', '89']</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI69" t="n">
         <v>2.2</v>
       </c>
-      <c r="M69" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N69" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O69" t="n">
-        <v>3</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T69" t="n">
-        <v>4</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X69" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ69" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45565.89583333334</v>
